--- a/artfynd/A 55656-2019 artfynd.xlsx
+++ b/artfynd/A 55656-2019 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 55656-2019 artfynd.xlsx
+++ b/artfynd/A 55656-2019 artfynd.xlsx
@@ -1152,7 +1152,7 @@
         <v>123552880</v>
       </c>
       <c r="B6" t="n">
-        <v>107596</v>
+        <v>107613</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1271,7 +1271,7 @@
         <v>123552926</v>
       </c>
       <c r="B7" t="n">
-        <v>56435</v>
+        <v>56441</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>

--- a/artfynd/A 55656-2019 artfynd.xlsx
+++ b/artfynd/A 55656-2019 artfynd.xlsx
@@ -1152,7 +1152,7 @@
         <v>123552880</v>
       </c>
       <c r="B6" t="n">
-        <v>107613</v>
+        <v>107631</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1271,7 +1271,7 @@
         <v>123552926</v>
       </c>
       <c r="B7" t="n">
-        <v>56441</v>
+        <v>56444</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>

--- a/artfynd/A 55656-2019 artfynd.xlsx
+++ b/artfynd/A 55656-2019 artfynd.xlsx
@@ -1149,10 +1149,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123552880</v>
+        <v>123552926</v>
       </c>
       <c r="B6" t="n">
-        <v>107631</v>
+        <v>56444</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1165,50 +1165,55 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>762</v>
+        <v>100070</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Hedblomster</t>
+          <t>Sandödla</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Helichrysum arenarium</t>
+          <t>Lacerta agilis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Moench</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>ex.</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>årsunge</t>
         </is>
       </c>
       <c r="L6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Sandåkra fd sandtag, Sk</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>421849</v>
+        <v>421895</v>
       </c>
       <c r="R6" t="n">
-        <v>6214537</v>
+        <v>6214511</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1241,6 +1246,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-03-28</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ny lokal! En juvenil sågs men hann inte fångas på bild. Prassel från ytterligare 2-3 ödlor noterades i slänten. Flera potentiella bohålor finns även om vegetationen är alltför tät.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1268,10 +1278,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123552926</v>
+        <v>123552880</v>
       </c>
       <c r="B7" t="n">
-        <v>56444</v>
+        <v>107633</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1284,55 +1294,50 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100070</v>
+        <v>762</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sandödla</t>
+          <t>Hedblomster</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lacerta agilis</t>
+          <t>Helichrysum arenarium</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Moench</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>ex.</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>årsunge</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Sandåkra fd sandtag, Sk</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>421895</v>
+        <v>421849</v>
       </c>
       <c r="R7" t="n">
-        <v>6214511</v>
+        <v>6214537</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1365,11 +1370,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-03-28</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ny lokal! En juvenil sågs men hann inte fångas på bild. Prassel från ytterligare 2-3 ödlor noterades i slänten. Flera potentiella bohålor finns även om vegetationen är alltför tät.</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 55656-2019 artfynd.xlsx
+++ b/artfynd/A 55656-2019 artfynd.xlsx
@@ -1149,10 +1149,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123552926</v>
+        <v>123552880</v>
       </c>
       <c r="B6" t="n">
-        <v>56444</v>
+        <v>107208</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1165,55 +1165,50 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100070</v>
+        <v>762</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sandödla</t>
+          <t>Hedblomster</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lacerta agilis</t>
+          <t>Helichrysum arenarium</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Moench</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>ex.</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>årsunge</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Sandåkra fd sandtag, Sk</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>421895</v>
+        <v>421849</v>
       </c>
       <c r="R6" t="n">
-        <v>6214511</v>
+        <v>6214537</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1246,11 +1241,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-03-28</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ny lokal! En juvenil sågs men hann inte fångas på bild. Prassel från ytterligare 2-3 ödlor noterades i slänten. Flera potentiella bohålor finns även om vegetationen är alltför tät.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1278,10 +1268,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123552880</v>
+        <v>123552926</v>
       </c>
       <c r="B7" t="n">
-        <v>107633</v>
+        <v>56444</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1294,50 +1284,55 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>762</v>
+        <v>100070</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Hedblomster</t>
+          <t>Sandödla</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Helichrysum arenarium</t>
+          <t>Lacerta agilis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Moench</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>ex.</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>årsunge</t>
         </is>
       </c>
       <c r="L7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Sandåkra fd sandtag, Sk</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>421849</v>
+        <v>421895</v>
       </c>
       <c r="R7" t="n">
-        <v>6214537</v>
+        <v>6214511</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1370,6 +1365,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-03-28</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ny lokal! En juvenil sågs men hann inte fångas på bild. Prassel från ytterligare 2-3 ödlor noterades i slänten. Flera potentiella bohålor finns även om vegetationen är alltför tät.</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 55656-2019 artfynd.xlsx
+++ b/artfynd/A 55656-2019 artfynd.xlsx
@@ -1149,10 +1149,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123552880</v>
+        <v>123552926</v>
       </c>
       <c r="B6" t="n">
-        <v>107208</v>
+        <v>56444</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1165,50 +1165,55 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>762</v>
+        <v>100070</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Hedblomster</t>
+          <t>Sandödla</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Helichrysum arenarium</t>
+          <t>Lacerta agilis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Moench</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>ex.</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>årsunge</t>
         </is>
       </c>
       <c r="L6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Sandåkra fd sandtag, Sk</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>421849</v>
+        <v>421895</v>
       </c>
       <c r="R6" t="n">
-        <v>6214537</v>
+        <v>6214511</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1241,6 +1246,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-03-28</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ny lokal! En juvenil sågs men hann inte fångas på bild. Prassel från ytterligare 2-3 ödlor noterades i slänten. Flera potentiella bohålor finns även om vegetationen är alltför tät.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1268,10 +1278,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123552926</v>
+        <v>123552880</v>
       </c>
       <c r="B7" t="n">
-        <v>56444</v>
+        <v>107208</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1284,55 +1294,50 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100070</v>
+        <v>762</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sandödla</t>
+          <t>Hedblomster</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lacerta agilis</t>
+          <t>Helichrysum arenarium</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Moench</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>ex.</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>årsunge</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Sandåkra fd sandtag, Sk</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>421895</v>
+        <v>421849</v>
       </c>
       <c r="R7" t="n">
-        <v>6214511</v>
+        <v>6214537</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1365,11 +1370,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-03-28</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ny lokal! En juvenil sågs men hann inte fångas på bild. Prassel från ytterligare 2-3 ödlor noterades i slänten. Flera potentiella bohålor finns även om vegetationen är alltför tät.</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 55656-2019 artfynd.xlsx
+++ b/artfynd/A 55656-2019 artfynd.xlsx
@@ -1149,10 +1149,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123552926</v>
+        <v>123552880</v>
       </c>
       <c r="B6" t="n">
-        <v>56444</v>
+        <v>107208</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1165,55 +1165,50 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100070</v>
+        <v>762</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sandödla</t>
+          <t>Hedblomster</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lacerta agilis</t>
+          <t>Helichrysum arenarium</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Moench</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>ex.</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>årsunge</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Sandåkra fd sandtag, Sk</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>421895</v>
+        <v>421849</v>
       </c>
       <c r="R6" t="n">
-        <v>6214511</v>
+        <v>6214537</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1246,11 +1241,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-03-28</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ny lokal! En juvenil sågs men hann inte fångas på bild. Prassel från ytterligare 2-3 ödlor noterades i slänten. Flera potentiella bohålor finns även om vegetationen är alltför tät.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1278,10 +1268,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123552880</v>
+        <v>123552926</v>
       </c>
       <c r="B7" t="n">
-        <v>107208</v>
+        <v>56444</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1294,50 +1284,55 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>762</v>
+        <v>100070</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Hedblomster</t>
+          <t>Sandödla</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Helichrysum arenarium</t>
+          <t>Lacerta agilis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Moench</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>ex.</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>årsunge</t>
         </is>
       </c>
       <c r="L7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Sandåkra fd sandtag, Sk</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>421849</v>
+        <v>421895</v>
       </c>
       <c r="R7" t="n">
-        <v>6214537</v>
+        <v>6214511</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1370,6 +1365,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-03-28</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ny lokal! En juvenil sågs men hann inte fångas på bild. Prassel från ytterligare 2-3 ödlor noterades i slänten. Flera potentiella bohålor finns även om vegetationen är alltför tät.</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 55656-2019 artfynd.xlsx
+++ b/artfynd/A 55656-2019 artfynd.xlsx
@@ -1152,7 +1152,7 @@
         <v>123552880</v>
       </c>
       <c r="B6" t="n">
-        <v>107208</v>
+        <v>107209</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
